--- a/AAII_Financials/Yearly/CSCO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CSCO_YR_FIN.xlsx
@@ -656,222 +656,234 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46228</v>
+      </c>
+      <c r="E7" s="2">
         <v>45864</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45500</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45136</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44772</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44408</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44037</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43673</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43309</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42945</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42581</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42210</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41846</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41482</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41118</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>63325000</v>
+      </c>
+      <c r="E8" s="3">
         <v>56654000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>53803000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>56998000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>51557000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>49818000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>49301000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>51904000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>49330000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>48005000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>49247000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>49161000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>47142000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>48607000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>46061000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>22465000</v>
+      </c>
+      <c r="E9" s="3">
         <v>19864000</v>
       </c>
-      <c r="E9" s="3">
-        <v>18975000</v>
-      </c>
       <c r="F9" s="3">
+        <v>18830000</v>
+      </c>
+      <c r="G9" s="3">
         <v>21245000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>19309000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17924000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17618000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19238000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18597000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>17781000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18287000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19480000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19373000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19167000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17852000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>40860000</v>
+      </c>
+      <c r="E10" s="3">
         <v>36790000</v>
       </c>
-      <c r="E10" s="3">
-        <v>34828000</v>
-      </c>
       <c r="F10" s="3">
+        <v>34973000</v>
+      </c>
+      <c r="G10" s="3">
         <v>35753000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>32248000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>31894000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>31683000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>32666000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>30733000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>30224000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>30960000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>29681000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>27769000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>29440000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>28209000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -890,56 +902,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>9563000</v>
+      </c>
+      <c r="E12" s="3">
         <v>9300000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7983000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7551000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6774000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6549000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6347000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6577000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6332000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6059000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6296000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6207000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6294000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5942000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5488000</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -985,105 +1001,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-682000</v>
+      </c>
+      <c r="E14" s="3">
         <v>674000</v>
       </c>
-      <c r="E14" s="3">
-        <v>1057000</v>
-      </c>
       <c r="F14" s="3">
+        <v>1202000</v>
+      </c>
+      <c r="G14" s="3">
         <v>721000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-411000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>587000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>361000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>350000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>228000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>766000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>484000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>418000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>105000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>316000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>916000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1028000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>698000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>282000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>313000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>215000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>141000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>150000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>221000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>259000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>303000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>359000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>275000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>395000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>371000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1099,104 +1124,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>47246000</v>
+      </c>
+      <c r="E17" s="3">
         <v>44138000</v>
       </c>
-      <c r="E17" s="3">
-        <v>40729000</v>
-      </c>
       <c r="F17" s="3">
+        <v>40584000</v>
+      </c>
+      <c r="G17" s="3">
         <v>41410000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>37533000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>36053000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>35179000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>37342000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36495000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>36032000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36587000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>38391000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37797000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37411000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35996000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>16079000</v>
+      </c>
+      <c r="E18" s="3">
         <v>12516000</v>
       </c>
-      <c r="E18" s="3">
-        <v>13074000</v>
-      </c>
       <c r="F18" s="3">
+        <v>13219000</v>
+      </c>
+      <c r="G18" s="3">
         <v>15588000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14024000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13765000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14122000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14562000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12835000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11973000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12660000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10770000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9345000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11196000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10065000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1215,88 +1247,92 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E20" s="3">
         <v>150000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>142000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>84000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>74000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>126000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>90000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>133000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1171000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>942000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>994000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>932000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>614000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>690000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>16847000</v>
+      </c>
+      <c r="E21" s="3">
         <v>13394000</v>
       </c>
-      <c r="E21" s="3">
-        <v>13630000</v>
-      </c>
       <c r="F21" s="3">
+        <v>13775000</v>
+      </c>
+      <c r="G21" s="3">
         <v>15786000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14263000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13880000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>14137000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14622000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12923000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15430000</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>24</v>
@@ -1307,156 +1343,168 @@
       <c r="P21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R21" s="3">
         <v>12963000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>1470000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1593000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1006000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>427000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>360000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>434000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>585000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>859000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>943000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>857000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>682000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>563000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>562000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>583000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>596000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>16009000</v>
+      </c>
+      <c r="E23" s="3">
         <v>11100000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12234000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15318000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14477000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>13262000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13970000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14571000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13039000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12287000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12920000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11201000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9715000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11227000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10159000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2742000</v>
+      </c>
+      <c r="E24" s="3">
         <v>920000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1914000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2705000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2665000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2671000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2756000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2950000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12929000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2678000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2181000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2220000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1862000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1244000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2118000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1502,105 +1550,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>13267000</v>
+      </c>
+      <c r="E26" s="3">
         <v>10180000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10320000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12613000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11812000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10591000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11214000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11621000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>110000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9609000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10739000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8981000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7853000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9983000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>8041000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>13267000</v>
+      </c>
+      <c r="E27" s="3">
         <v>10180000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10320000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12613000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11812000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10591000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11214000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11621000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>110000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9609000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10739000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8981000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7853000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>9983000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>8041000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1646,9 +1703,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1676,8 +1736,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
@@ -1694,9 +1754,12 @@
       <c r="Q29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1742,9 +1805,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1790,105 +1856,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-150000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-142000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-84000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-74000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-126000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-90000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-133000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1171000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-942000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-994000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-932000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-614000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-690000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13267000</v>
+      </c>
+      <c r="E33" s="3">
         <v>10180000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10320000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12613000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11812000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10591000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11214000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11621000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>110000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9609000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10739000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8981000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7853000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9983000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>8041000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1934,110 +2009,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13267000</v>
+      </c>
+      <c r="E35" s="3">
         <v>10180000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10320000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12613000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11812000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10591000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11214000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11621000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>110000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9609000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10739000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8981000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7853000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9983000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>8041000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46228</v>
+      </c>
+      <c r="E38" s="2">
         <v>45864</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45500</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45136</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44772</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44408</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44037</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43673</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43309</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42945</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42581</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42210</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41846</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41482</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41118</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2056,8 +2140,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2076,440 +2161,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7218000</v>
+      </c>
+      <c r="E41" s="3">
         <v>8346000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7508000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10123000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7079000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9175000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11809000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11750000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8934000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11708000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7631000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6877000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6726000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7925000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9799000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8700000</v>
+      </c>
+      <c r="E42" s="3">
         <v>8327000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11096000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>16211000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12188000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>15352000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17616000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>21663000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>37614000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>58784000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>58125000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>53539000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>45348000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>42685000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>38917000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12762000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11462000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11423000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9206000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10527000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10146000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10523000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10586000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12003000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10002000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10119000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9835000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9310000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9507000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8030000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5694000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3164000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3373000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3644000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2568000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1559000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1282000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1383000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1846000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1616000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1217000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1627000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1591000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1476000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1663000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4282000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3123000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2697000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3973000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4355000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2866000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2343000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2352000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1408000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1593000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1627000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4405000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4139000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3928000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3524000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>38665000</v>
+      </c>
+      <c r="E46" s="3">
         <v>34986000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>36862000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>43348000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>36717000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>39112000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>43573000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>47755000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>61837000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>83703000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>78719000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>73368000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>67114000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>65521000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>61933000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1900000</v>
+        <v>3299000</v>
       </c>
       <c r="E47" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="F47" s="3">
         <v>2363000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3113000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3400000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>849000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>169000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1275000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1096000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5721000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5161000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4755000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4817000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4744000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4443000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4155000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3414000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3156000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3056000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3000000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3433000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3374000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2789000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3006000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3322000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3506000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3332000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3252000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3322000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3402000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>67034000</v>
+      </c>
+      <c r="E49" s="3">
         <v>68311000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>69879000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>40353000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>40873000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>41787000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>35382000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>35730000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>34258000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>32305000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>29126000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>26845000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>27519000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>25322000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>18957000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2555,9 +2668,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2603,57 +2719,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1358000</v>
+        <v>2866000</v>
       </c>
       <c r="E52" s="3">
+        <v>1238000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1215000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1923000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1554000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3072000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2651000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1221000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>486000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4767000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5140000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5485000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2368000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2282000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3024000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2699,57 +2821,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>129637000</v>
+      </c>
+      <c r="E54" s="3">
         <v>122291000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>124413000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>101852000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>94002000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>97497000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>94853000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>97793000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>108784000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>129818000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>121652000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>113373000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>105070000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>101191000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>91759000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2768,8 +2896,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2788,296 +2917,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3660000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2734000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2802000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2842000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2594000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2513000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2359000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2188000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2063000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1385000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1056000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1104000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1032000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1029000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>859000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10565000</v>
+      </c>
+      <c r="E58" s="3">
         <v>5607000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11716000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2063000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1421000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2845000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3346000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10192000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5248000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7992000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4160000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3897000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>508000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3283000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>31000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23243000</v>
+      </c>
+      <c r="E59" s="3">
         <v>23112000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22458000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22420000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18309000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17081000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16504000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16111000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16738000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18206000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19695000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18411000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18269000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17684000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16841000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41525000</v>
+      </c>
+      <c r="E60" s="3">
         <v>35064000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>40584000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>31309000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25640000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26257000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25331000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>31712000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27035000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27583000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>24911000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>23412000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19809000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21996000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17731000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>20620000</v>
+      </c>
+      <c r="E61" s="3">
         <v>24036000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>20527000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7389000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9150000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9849000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12239000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14475000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20393000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25725000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>24483000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21457000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20337000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12928000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>16297000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4329000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3910000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5543000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7097000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8904000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9966000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10242000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10141000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9816000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10373000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8673000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8797000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8263000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7139000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6430000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3123,9 +3271,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3171,9 +3322,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3219,57 +3373,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>79352000</v>
+      </c>
+      <c r="E66" s="3">
         <v>75448000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>78956000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>57499000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>54229000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>56222000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>56933000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>64222000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>65580000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>63681000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>58066000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53675000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>48416000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>42071000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>40473000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3288,8 +3448,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3335,9 +3496,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3383,9 +3547,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3431,9 +3598,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3479,57 +3649,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1565000</v>
+      </c>
+      <c r="E72" s="3">
         <v>50000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1087000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1639000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1319000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-654000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2763000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5903000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1233000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20838000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19396000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16045000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14093000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16215000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11354000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3575,9 +3751,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3623,9 +3802,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3671,57 +3853,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50285000</v>
+      </c>
+      <c r="E76" s="3">
         <v>46843000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>45457000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>44353000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>39773000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>41275000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>37920000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>33571000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>43204000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>66137000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>63586000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>59698000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>56654000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>59120000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>51286000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3767,110 +3955,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46228</v>
+      </c>
+      <c r="E80" s="2">
         <v>45864</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45500</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45136</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44772</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44408</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44037</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43673</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43309</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42945</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42581</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42210</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41846</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41482</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41118</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13267000</v>
+      </c>
+      <c r="E81" s="3">
         <v>10180000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10320000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12613000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11812000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10591000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11214000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11621000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>110000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9609000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10739000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8981000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7853000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9983000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>8041000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3889,8 +4086,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3904,25 +4102,25 @@
         <v>700000</v>
       </c>
       <c r="G83" s="3">
-        <v>800000</v>
+        <v>700000</v>
       </c>
       <c r="H83" s="3">
         <v>800000</v>
       </c>
       <c r="I83" s="3">
+        <v>800000</v>
+      </c>
+      <c r="J83" s="3">
         <v>900000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1000000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1100000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2286000</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>24</v>
@@ -3933,12 +4131,15 @@
       <c r="P83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R83" s="3">
         <v>2208000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3984,9 +4185,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4032,9 +4236,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4080,9 +4287,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4128,9 +4338,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4176,57 +4389,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14177000</v>
+      </c>
+      <c r="E89" s="3">
         <v>14193000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10880000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>19886000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13226000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15454000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15426000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15831000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13666000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13876000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12552000</v>
-      </c>
-      <c r="N89" s="3">
-        <v>12332000</v>
       </c>
       <c r="O89" s="3">
         <v>12332000</v>
       </c>
       <c r="P89" s="3">
+        <v>12332000</v>
+      </c>
+      <c r="Q89" s="3">
         <v>12894000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>11491000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4245,56 +4464,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1410000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-905000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-670000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-849000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-477000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-692000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-770000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-909000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-834000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-964000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1227000</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-1275000</v>
       </c>
       <c r="O91" s="3">
         <v>-1275000</v>
       </c>
       <c r="P91" s="3">
+        <v>-1275000</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1160000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1126000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4340,9 +4563,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4388,41 +4614,44 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3484000</v>
+      </c>
+      <c r="E94" s="3">
         <v>1733000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-20478000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5107000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1553000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5285000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3500000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>14837000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>15318000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6036000</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>24</v>
@@ -4433,12 +4662,15 @@
       <c r="P94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R94" s="3">
         <v>-3815000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4457,56 +4689,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>6553000</v>
+      </c>
+      <c r="E96" s="3">
         <v>6437000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>6384000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>6302000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>6224000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>6163000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>6016000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>5979000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>5968000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-5511000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-4086000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-3758000</v>
       </c>
       <c r="O96" s="3">
         <v>-3758000</v>
       </c>
       <c r="P96" s="3">
+        <v>-3758000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-3310000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1501000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4552,9 +4788,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4600,9 +4839,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4648,41 +4890,44 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12347000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-15815000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6844000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11626000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-15962000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12097000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-18856000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-27889000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-31764000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3806000</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>24</v>
@@ -4693,35 +4938,38 @@
       <c r="P100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R100" s="3">
         <v>-5539000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-43000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-31000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-105000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-180000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>58000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-30000</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>24</v>
@@ -4741,58 +4989,64 @@
       <c r="P101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1683000</v>
+      </c>
+      <c r="E102" s="3">
         <v>68000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2785000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3048000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1363000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1870000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>40000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2779000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2780000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4034000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>151000</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-1199000</v>
       </c>
       <c r="O102" s="3">
         <v>-1199000</v>
       </c>
       <c r="P102" s="3">
+        <v>-1199000</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-1874000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2137000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
